--- a/artfynd/A 40482-2025 artfynd.xlsx
+++ b/artfynd/A 40482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114565475</v>
+        <v>114565472</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620120</v>
+        <v>620214</v>
       </c>
       <c r="R2" t="n">
-        <v>6936509</v>
+        <v>6936488</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -777,19 +772,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114565476</v>
+        <v>114565475</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620100</v>
+        <v>620120</v>
       </c>
       <c r="R3" t="n">
-        <v>6936530</v>
+        <v>6936509</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114565472</v>
+        <v>114565476</v>
       </c>
       <c r="B4" t="n">
-        <v>78541</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620214</v>
+        <v>620100</v>
       </c>
       <c r="R4" t="n">
-        <v>6936488</v>
+        <v>6936530</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>114565452</v>
+        <v>114565477</v>
       </c>
       <c r="B5" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620402</v>
+        <v>620070</v>
       </c>
       <c r="R5" t="n">
-        <v>6936459</v>
+        <v>6936487</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>114565448</v>
+        <v>114565473</v>
       </c>
       <c r="B6" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221946</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620520</v>
+        <v>620181</v>
       </c>
       <c r="R6" t="n">
-        <v>6936442</v>
+        <v>6936481</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1185,50 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>114565453</v>
+        <v>121668126</v>
       </c>
       <c r="B7" t="n">
-        <v>96613</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lappmon, Mpd</t>
+          <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620400</v>
+        <v>620286</v>
       </c>
       <c r="R7" t="n">
-        <v>6936460</v>
+        <v>6936439</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1255,12 +1225,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,54 +1267,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>114565446</v>
+        <v>121668125</v>
       </c>
       <c r="B8" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79406</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>864</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lappmon, Mpd</t>
+          <t>Kontorillen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620546</v>
+        <v>620301</v>
       </c>
       <c r="R8" t="n">
-        <v>6936411</v>
+        <v>6936442</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1361,12 +1332,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-25</t>
+          <t>2024-10-16</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1393,15 +1374,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>114565451</v>
+        <v>114565446</v>
       </c>
       <c r="B9" t="n">
-        <v>97567</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1428,7 +1404,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1437,10 +1413,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620409</v>
+        <v>620546</v>
       </c>
       <c r="R9" t="n">
-        <v>6936465</v>
+        <v>6936411</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1499,50 +1475,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121668125</v>
+        <v>114565451</v>
       </c>
       <c r="B10" t="n">
-        <v>78714</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>864</v>
+        <v>219790</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kontorillen, Mpd</t>
+          <t>Lappmon, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620301</v>
+        <v>620409</v>
       </c>
       <c r="R10" t="n">
-        <v>6936442</v>
+        <v>6936465</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1569,22 +1544,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2023-08-25</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,6 +1573,394 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>114565452</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lappmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>620402</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6936459</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>114565448</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lappmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>620520</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6936442</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>114565449</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lappmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>620499</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6936457</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>114565453</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lappmon, Mpd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>620400</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6936460</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Timrå</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-08-25</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Alexandra Holmgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40482-2025 artfynd.xlsx
+++ b/artfynd/A 40482-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565472</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565475</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565476</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565477</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565473</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1264,6 +1294,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668126</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1371,6 +1406,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121668125</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1472,6 +1512,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565446</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565451</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565452</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1767,6 +1822,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565448</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1864,6 +1924,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565449</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1961,8 +2026,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114565453</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>